--- a/site/ValueSet-vs-diagnostico-consulta.xlsx
+++ b/site/ValueSet-vs-diagnostico-consulta.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T15:20:04-03:00</t>
+    <t>2026-10-06T01:23:13-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -66,6 +66,12 @@
     <t>AGESIC</t>
   </si>
   <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>AGESIC (https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/salud-digital)</t>
+  </si>
+  <si>
     <t>Jurisdiction</t>
   </si>
   <si>
@@ -75,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Diagnósticos: miembros del refset SNOMED CT-UY 261341000179103 (SNOMED CT edición Uruguay).
-El listado completo de conceptos puede consultarse en el [navegador SNOMED CT-UY](https://snomedbrowser.org/?perspective=full&amp;conceptId1=261341000179103&amp;edition=MAIN/SNOMEDCT-ES/SNOMEDCT-UY/2026-06-15&amp;release=&amp;languages=es,en).</t>
+    <t>Diagnósticos: listado de códigos SNOMED CT de prueba (docs/Códigos para prueba FHIR.xlsx, pestaña Dg).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -91,16 +96,67 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>concept</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>261341000179103</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>27337007</t>
+  </si>
+  <si>
+    <t>extrasístoles ventriculares unifocales</t>
+  </si>
+  <si>
+    <t>38341003</t>
+  </si>
+  <si>
+    <t>hipertensión arterial (trastorno)</t>
+  </si>
+  <si>
+    <t>302866003</t>
+  </si>
+  <si>
+    <t>hipoglicemia (trastorno)</t>
+  </si>
+  <si>
+    <t>235595009</t>
+  </si>
+  <si>
+    <t>enfermedad por reflujo gastroesofágico (trastorno)</t>
+  </si>
+  <si>
+    <t>446221000</t>
+  </si>
+  <si>
+    <t>insuficiencia cardíaca con fracción de eyección conservada (trastorno)</t>
+  </si>
+  <si>
+    <t>398057008</t>
+  </si>
+  <si>
+    <t>cefalea de tipo tensional (trastorno)</t>
+  </si>
+  <si>
+    <t>4556007</t>
+  </si>
+  <si>
+    <t>gastritis (trastorno)</t>
+  </si>
+  <si>
+    <t>413838009</t>
+  </si>
+  <si>
+    <t>cardiopatía isquémica crónica (trastorno)</t>
+  </si>
+  <si>
+    <t>1381430004</t>
+  </si>
+  <si>
+    <t>angina de pecho sin obstrucción de arterias coronarias (trastorno)</t>
+  </si>
+  <si>
+    <t>1085006</t>
+  </si>
+  <si>
+    <t>candidiasis de la vulva (trastorno)</t>
   </si>
   <si>
     <t>System URI</t>
@@ -240,7 +296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -337,20 +393,28 @@
       <c r="A12" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s" s="2">
         <v>24</v>
+      </c>
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -360,7 +424,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -369,40 +433,106 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/site/ValueSet-vs-diagnostico-consulta.xlsx
+++ b/site/ValueSet-vs-diagnostico-consulta.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
